--- a/business_forms/028_key_account_planning_survey--business_forms.xlsx
+++ b/business_forms/028_key_account_planning_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -815,8 +815,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,12 +844,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'revenue_growth'}</t>
+          <t>revenue_growth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Revenue Growth'}</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'customer_acquisition'}</t>
+          <t>customer_acquisition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Customer Acquisition'}</t>
+          <t>Customer Acquisition</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retention'}</t>
+          <t>retention</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retention'}</t>
+          <t>Retention</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales_team'}</t>
+          <t>sales_team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales Team'}</t>
+          <t>Sales Team</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'increase_revenue'}</t>
+          <t>increase_revenue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Increase Revenue'}</t>
+          <t>Increase Revenue</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'enhance_customer_experience'}</t>
+          <t>enhance_customer_experience</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Enhance Customer Experience'}</t>
+          <t>Enhance Customer Experience</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'won'}</t>
+          <t>won</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Won'}</t>
+          <t>Won</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lost'}</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lost'}</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
